--- a/src/utils/spreadsheet/fixtures/palette.xlsx
+++ b/src/utils/spreadsheet/fixtures/palette.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t xml:space="preserve">Sample palette</t>
   </si>
@@ -38,6 +38,15 @@
     <t xml:space="preserve">Note</t>
   </si>
   <si>
+    <t xml:space="preserve">Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer</t>
+  </si>
+  <si>
     <t xml:space="preserve">brick red</t>
   </si>
   <si>
@@ -53,6 +62,9 @@
     <t xml:space="preserve">2E8B57</t>
   </si>
   <si>
+    <t xml:space="preserve">Slate Blue</t>
+  </si>
+  <si>
     <t xml:space="preserve">mustard</t>
   </si>
   <si>
@@ -83,7 +95,7 @@
     <t xml:space="preserve">Ωmega teal</t>
   </si>
   <si>
-    <t xml:space="preserve">#2a9d8f</t>
+    <t xml:space="preserve">rgba(42, 157, 143, 0.6)</t>
   </si>
   <si>
     <t xml:space="preserve">wash</t>
@@ -294,7 +306,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -315,89 +327,125 @@
       <c r="D3" s="0" t="s">
         <v>4</v>
       </c>
+      <c r="E3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>2.5</v>
       </c>
+      <c r="E5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E6" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D7" s="0" t="n">
         <f aca="false">1/4</f>
         <v>0.25</v>
       </c>
+      <c r="E7" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -421,12 +469,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
